--- a/test_cases/default_test_cases.xlsx
+++ b/test_cases/default_test_cases.xlsx
@@ -10,7 +10,7 @@
     <sheet name="TestCases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TestCases'!$A$1:$J$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TestCases'!$A$1:$J$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1623,32 +1623,32 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GLB-001</t>
+          <t>VAL-018</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>PayloadKey</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Vulnerability</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Malformed JSON body</t>
+          <t>NoSQL injection (operator object)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>special_chars</t>
+          <t>nosql_injection</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>{invalid_json: }</t>
+          <t>{"$ne":null}</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>API should reject malformed JSON</t>
+          <t>API should reject NoSQL operator injection</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1675,53 +1675,733 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>GLB-001</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Malformed JSON body</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>malformed_json</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>{invalid_json: }</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>400-499</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>API should reject malformed JSON</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>GLB-002</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Auth</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Auth token missing (Bearer)</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>auth_token_missing</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>401-401</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>API should reject missing auth header</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>GLB-003</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Baseline valid request</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>200-200</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Valid request should return the expected success code</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>GLB-004</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Invalid pagination parameter (page=-1)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>query_param_invalid</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>page:-1</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>400-499</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>API should reject invalid pagination values</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>GLB-005</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Invalid filter value (status=xyz)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>query_param_invalid</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>status:xyz</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>400-499</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>API should validate filter values</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>GLB-006</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>SQL injection in query parameter</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>query_param_inject</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>page:' OR '1'='1</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>400-499</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>API should reject SQL injection in query params</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>GLB-007</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported HTTP method (DELETE)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>method_change</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>400-499</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>API should reject unsupported methods with 405</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>GLB-008</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Mass assignment (role=admin)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>inject_extra_key</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>role:admin</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>200-200</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>API should ignore hidden/mass-assignment keys</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>GLB-009</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Security headers (CSP/HSTS/X-Content-Type-Options)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>security_headers_check</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>API should send security headers</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>GLB-010</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>CORS misconfiguration (evil Origin)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>cors_check</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>https://evil.example.com</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>API must not reflect untrusted origins in Access-Control-Allow-Origin</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>GLB-011</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Sensitive data exposure in response</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>sensitive_data_scan</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Responses must not leak passwords/tokens/OTP</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>GLB-012</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Error information leakage</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>error_leak_scan</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>400-499</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Error responses must not expose stack traces or internals</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>GLB-013</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Response schema validation</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>schema_validation</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Response should match the declared schema</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>GLB-014</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Performance within SLA</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>performance_check</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Response time should be within the SLA</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>GLB-015</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate submission prevention</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>duplicate_submit</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>400-499</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate payloads should be rejected</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J25"/>
+  <autoFilter ref="A1:J39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>